--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>96.14342595309539</v>
+        <v>15.623306717378</v>
       </c>
       <c r="D2" t="n">
-        <v>96.23618328636215</v>
+        <v>15.63837978403385</v>
       </c>
       <c r="E2" t="n">
-        <v>29.85716189924844</v>
+        <v>4.851788808627871</v>
       </c>
       <c r="F2" t="n">
-        <v>31.90241514122912</v>
+        <v>5.184142460449733</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>81.06973107068285</v>
+        <v>13.17383129898596</v>
       </c>
       <c r="D3" t="n">
-        <v>81.20766983425229</v>
+        <v>13.196246348066</v>
       </c>
       <c r="E3" t="n">
-        <v>29.85716189924844</v>
+        <v>4.851788808627871</v>
       </c>
       <c r="F3" t="n">
-        <v>31.90241514122912</v>
+        <v>5.184142460449733</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.20796371455301</v>
+        <v>3.771294103614865</v>
       </c>
       <c r="D4" t="n">
-        <v>20.26807354659669</v>
+        <v>3.293561951321962</v>
       </c>
       <c r="E4" t="n">
-        <v>29.85716189924844</v>
+        <v>4.851788808627871</v>
       </c>
       <c r="F4" t="n">
-        <v>31.90241514122912</v>
+        <v>5.184142460449733</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.86860279114362</v>
+        <v>9.72864795356084</v>
       </c>
       <c r="D5" t="n">
-        <v>44.83388406656094</v>
+        <v>7.285506160816153</v>
       </c>
       <c r="E5" t="n">
-        <v>29.85716189924844</v>
+        <v>4.851788808627871</v>
       </c>
       <c r="F5" t="n">
-        <v>31.90241514122912</v>
+        <v>5.184142460449733</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.4077968551477</v>
+        <v>3.641266988961501</v>
       </c>
       <c r="D6" t="n">
-        <v>17.06212744307034</v>
+        <v>2.77259570949893</v>
       </c>
       <c r="E6" t="n">
-        <v>29.85716189924844</v>
+        <v>4.851788808627871</v>
       </c>
       <c r="F6" t="n">
-        <v>31.90241514122912</v>
+        <v>5.184142460449733</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
